--- a/data/nzd0085/nzd0085.xlsx
+++ b/data/nzd0085/nzd0085.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D323"/>
+  <dimension ref="A1:D324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6244,6 +6244,24 @@
         <v>349.07</v>
       </c>
       <c r="D323" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>353.32</v>
+      </c>
+      <c r="C324" t="n">
+        <v>347.68</v>
+      </c>
+      <c r="D324" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6260,7 +6278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B373"/>
+  <dimension ref="A1:B374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9993,6 +10011,16 @@
       </c>
       <c r="B373" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -10161,28 +10189,28 @@
         <v>0.0902</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2443441895625809</v>
+        <v>0.2416402228606062</v>
       </c>
       <c r="J2" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K2" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1633857114999355</v>
+        <v>0.1608498843958353</v>
       </c>
       <c r="M2" t="n">
-        <v>3.162786606585803</v>
+        <v>3.16497948399721</v>
       </c>
       <c r="N2" t="n">
-        <v>16.21775345666307</v>
+        <v>16.22292262652223</v>
       </c>
       <c r="O2" t="n">
-        <v>4.027127196484247</v>
+        <v>4.027768939068157</v>
       </c>
       <c r="P2" t="n">
-        <v>351.0291822714089</v>
+        <v>351.0588067372327</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -10243,28 +10271,28 @@
         <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2549268643412421</v>
+        <v>0.2513269546810933</v>
       </c>
       <c r="J3" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K3" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1919908987434225</v>
+        <v>0.1876540682901052</v>
       </c>
       <c r="M3" t="n">
-        <v>2.812773828448631</v>
+        <v>2.819270699408979</v>
       </c>
       <c r="N3" t="n">
-        <v>14.50916023764422</v>
+        <v>14.56239810314449</v>
       </c>
       <c r="O3" t="n">
-        <v>3.809089161157063</v>
+        <v>3.816071029625168</v>
       </c>
       <c r="P3" t="n">
-        <v>346.5146418793436</v>
+        <v>346.5540822321475</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10302,7 +10330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D323"/>
+  <dimension ref="A1:D324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17411,6 +17439,28 @@
         </is>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>-35.51149076324277,174.47752800425886</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>-35.511677863438685,174.47839931308442</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0085/nzd0085.xlsx
+++ b/data/nzd0085/nzd0085.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D324"/>
+  <dimension ref="A1:D326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6262,6 +6262,42 @@
         <v>347.68</v>
       </c>
       <c r="D324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>352.35</v>
+      </c>
+      <c r="C325" t="n">
+        <v>346.07</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>354.66</v>
+      </c>
+      <c r="C326" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="D326" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6278,7 +6314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B374"/>
+  <dimension ref="A1:B376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10021,6 +10057,26 @@
       </c>
       <c r="B374" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -10189,28 +10245,28 @@
         <v>0.0902</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2416402228606062</v>
+        <v>0.23657084233328</v>
       </c>
       <c r="J2" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1608498843958353</v>
+        <v>0.1561737383672347</v>
       </c>
       <c r="M2" t="n">
-        <v>3.16497948399721</v>
+        <v>3.168085890484081</v>
       </c>
       <c r="N2" t="n">
-        <v>16.22292262652223</v>
+        <v>16.22964840721977</v>
       </c>
       <c r="O2" t="n">
-        <v>4.027768939068157</v>
+        <v>4.028603778881682</v>
       </c>
       <c r="P2" t="n">
-        <v>351.0588067372327</v>
+        <v>351.1145110586788</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -10271,28 +10327,28 @@
         <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2513269546810933</v>
+        <v>0.2434010159889174</v>
       </c>
       <c r="J3" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K3" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1876540682901052</v>
+        <v>0.1776568046074624</v>
       </c>
       <c r="M3" t="n">
-        <v>2.819270699408979</v>
+        <v>2.834933862615641</v>
       </c>
       <c r="N3" t="n">
-        <v>14.56239810314449</v>
+        <v>14.71830092042133</v>
       </c>
       <c r="O3" t="n">
-        <v>3.816071029625168</v>
+        <v>3.836443785645937</v>
       </c>
       <c r="P3" t="n">
-        <v>346.5540822321475</v>
+        <v>346.6411810079046</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10330,7 +10386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D324"/>
+  <dimension ref="A1:D326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17461,6 +17517,50 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>-35.51149936755661,174.4775260986848</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>-35.511692144836275,174.47839615031822</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>-35.51147887687101,174.47753063670072</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>-35.51167591194336,174.4783997452636</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0085/nzd0085.xlsx
+++ b/data/nzd0085/nzd0085.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D326"/>
+  <dimension ref="A1:D327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6298,6 +6298,24 @@
         <v>347.9</v>
       </c>
       <c r="D326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>355.6</v>
+      </c>
+      <c r="C327" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="D327" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6314,7 +6332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B376"/>
+  <dimension ref="A1:B377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10077,6 +10095,16 @@
       </c>
       <c r="B376" t="n">
         <v>0.48</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>-0.44</v>
       </c>
     </row>
   </sheetData>
@@ -10245,28 +10273,28 @@
         <v>0.0902</v>
       </c>
       <c r="I2" t="n">
-        <v>0.23657084233328</v>
+        <v>0.2353837528273123</v>
       </c>
       <c r="J2" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K2" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1561737383672347</v>
+        <v>0.1556763212614533</v>
       </c>
       <c r="M2" t="n">
-        <v>3.168085890484081</v>
+        <v>3.163693528983742</v>
       </c>
       <c r="N2" t="n">
-        <v>16.22964840721977</v>
+        <v>16.19074484567879</v>
       </c>
       <c r="O2" t="n">
-        <v>4.028603778881682</v>
+        <v>4.023772464451586</v>
       </c>
       <c r="P2" t="n">
-        <v>351.1145110586788</v>
+        <v>351.1276088172033</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -10327,28 +10355,28 @@
         <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2434010159889174</v>
+        <v>0.2404550466439329</v>
       </c>
       <c r="J3" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K3" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1776568046074624</v>
+        <v>0.1744716743513215</v>
       </c>
       <c r="M3" t="n">
-        <v>2.834933862615641</v>
+        <v>2.83852246904837</v>
       </c>
       <c r="N3" t="n">
-        <v>14.71830092042133</v>
+        <v>14.7401634030527</v>
       </c>
       <c r="O3" t="n">
-        <v>3.836443785645937</v>
+        <v>3.839292044511944</v>
       </c>
       <c r="P3" t="n">
-        <v>346.6411810079046</v>
+        <v>346.673685376705</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10386,7 +10414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D326"/>
+  <dimension ref="A1:D327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17561,6 +17589,28 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>-35.5114705386699,174.47753248333865</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>-35.51167058968335,174.47840092393392</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
